--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-patient.xlsx
@@ -371,7 +371,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -677,7 +677,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1446,7 +1446,7 @@
     <t>人の国内パートナーシップの状況。 / The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1590,7 +1590,7 @@
     <t>その患者の患者と接触者との関係の性質。 / The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>code</t>
@@ -2229,7 +2229,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
